--- a/deliverables/迪拜沙龙-执行推进表.xlsx
+++ b/deliverables/迪拜沙龙-执行推进表.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-沙龙议程" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-合作单位联络推进" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-开发商嘉宾筛选" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-邀约名单管理" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-待办事项跟踪" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-预算估算" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-三视角策略" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-沙龙议程" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-合作单位联络推进" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-开发商嘉宾筛选" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-邀约名单管理" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-待办事项跟踪" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-预算估算" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,25 +32,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
+      <name val="微软雅黑"/>
       <b val="1"/>
-      <color rgb="000B1F3A"/>
+      <color rgb="002A144A"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
+      <name val="微软雅黑"/>
       <sz val="10.5"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
+      <name val="微软雅黑"/>
       <i val="1"/>
-      <color rgb="007A6A3C"/>
+      <color rgb="006A4E9A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -62,17 +63,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5EFE0"/>
+        <fgColor rgb="00EDE4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B1F3A"/>
+        <fgColor rgb="002A144A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF0F5"/>
+        <fgColor rgb="00F3EEFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -484,6 +485,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>活动策划三视角策略表（观众 / 热点 / 利益）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>视角</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>核心问题</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>策略要点</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>对应沙龙动作</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落地负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>观众视角</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>如何让对的人愿意来？</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>精准邀约、低门槛入场、高规格体验、稀缺社交价值；把“被推销的顾虑”变成“怕错过的期待”</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>15席闭门限定 + 联名邀请函 + 一对一电话邀约 + 会前预热资料 + 老客带客礼遇</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>（活动负责人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>观众视角</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>来了如何有获得感？</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>现场即时价值：CRS自测、资产诊断、一手项目信息</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>设三张主题桌（身份/算力/房产），茶歇定向撮合客户与嘉宾</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>（活动负责人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>热点视角</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>凭什么被关注？</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>用全民赚钱话题与真实焦虑做钩子：美股收益、CRS落地、AI算力出海</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>开场美股收益复盘 → CRS追缴案例 → 迪拜算力洼地；世界杯/油价暖场</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>（内容负责人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>热点视角</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>如何卡准窗口、规避风险？</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>热点只做引子，敏感话题借壳包装；地缘冲突仅作背景（流量红利已过，不硬蹭）</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>以“全球资产配置/国际教育”外壳包装；不承诺避税，讲合法规划与申报</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>（合规）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>利益视角</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>投资人能赚到什么？</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>身份即资产（零个税/美元/保值隔离）、捡漏窗口、算力产业入口、风险对冲</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>对比表 + 收益可视化案例（购房签证/法拍别墅7-8折/算力投资）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>（内容负责人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>利益视角</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>渠道方与主办方如何获利？</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>补齐迪拜产品线、共享客源、考察团与签约分成、联名背书沉淀客户资产</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>与移民/金融/律所约定分成机制；系列化活动持续转化</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>（负责人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>设计原则：观众为起点（愿意来）、热点为引信（被关注）、利益为落点（能获益）。三视角贯穿PPT与全部执行环节。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -814,7 +1043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1222,7 +1451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1538,7 +1767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1964,7 +2193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2448,7 +2677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
